--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_必要資料の優先順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_必要資料の優先順位_20261015.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8/13 S1・S2</t>
+          <t>8/13 S1・S2　令和8年10月15日 受領</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8/13 S3</t>
+          <t>8/13 S3　取崩額・積立額は受領。残高が未着</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8/13 S欄（一部）</t>
+          <t>8/13 S欄　令和8年10月15日 受領</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_必要資料の優先順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_必要資料の優先順位_20261015.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア者・重症心身障害者を含む）、医療的ケア児等コーディネーターの配置状況、強度行動障害の状態にある方の人数と支援体制</t>
+          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア児等・重症心身障害者を含む）、医療的ケア児等コーディネーターの配置状況、強度行動障害の状態にある方の人数と支援体制</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_必要資料の優先順位_20261015.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_必要資料の優先順位_20261015.xlsx
@@ -933,17 +933,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>保険料基準額が240円動く。 取崩なし6,048円／12,000千円全額6,000円弱／第9期と同じ35,000千円5,808円</t>
+          <t>保険料基準額が1,719円動く。 取崩なし6,053円／105,000千円（令和8年度末見込の半分）5,194円／210,000千円（全額）4,334円</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>年報 様式4 の12,000千円を保守的な前提として置き、取崩なしのケースを標準にしている</t>
+          <t>町の財務書類の残高（令和5年度末120,000千円、令和8年度末見込210,000千円）を前提に、取崩なしのケースを標準にしている</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8/13 S3　取崩額・積立額は受領。残高が未着</t>
+          <t>8/13 S3　取崩額・積立額は受領。10/21 令和5年度末までの残高を町の財務書類で確認。令和7年度末の残高が未着</t>
         </is>
       </c>
     </row>
